--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 11:27</t>
+    <t xml:space="preserve">2026-09-09 19:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:04</t>
+    <t xml:space="preserve">2026-09-17 04:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:21</t>
+    <t xml:space="preserve">2026-09-25 11:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 11:15</t>
+    <t xml:space="preserve">2026-09-26 23:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t xml:space="preserve">Territorio</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Reg_Mujeres</t>
   </si>
   <si>
-    <t xml:space="preserve">Magallanes y la Antartica Chilena</t>
+    <t xml:space="preserve">Magallanes</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-26 23:49</t>
+    <t xml:space="preserve">2026-10-05 04:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Magallanes y la Antartica Chilena</t>
+    <t xml:space="preserve">Region de Magallanes</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magallanes</t>
   </si>
   <si>
     <t xml:space="preserve">Última Esperanza</t>
@@ -472,7 +469,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="35.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
@@ -726,7 +723,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>121</v>
@@ -737,7 +734,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>124</v>
@@ -748,7 +745,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>122</v>
@@ -759,7 +756,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>123</v>
